--- a/docs/workbook-split/dateien/Jahresabschluss.xlsx
+++ b/docs/workbook-split/dateien/Jahresabschluss.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -703,9 +702,10 @@
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="7" t="n"/>
       <c r="K7" s="7" t="n"/>
-      <c r="L7" s="1">
-        <f>IF(H7="nicht erforderlich","Entfällt",IF(AND(H7="vollständig",J7&lt;&gt;""),"Vollständig",IF(AND(H7="vollständig",J7=""),"Dokument fehlt",IF(AND(ISNUMBER(I7),I7&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M7" s="1" t="n"/>
       <c r="N7" s="1" t="n"/>
@@ -745,9 +745,10 @@
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="n"/>
-      <c r="L8" s="1">
-        <f>IF(H8="nicht erforderlich","Entfällt",IF(AND(H8="vollständig",J8&lt;&gt;""),"Vollständig",IF(AND(H8="vollständig",J8=""),"Dokument fehlt",IF(AND(ISNUMBER(I8),I8&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M8" s="1" t="n"/>
       <c r="N8" s="1" t="n"/>
@@ -787,9 +788,10 @@
       <c r="I9" s="8" t="n"/>
       <c r="J9" s="7" t="n"/>
       <c r="K9" s="7" t="n"/>
-      <c r="L9" s="1">
-        <f>IF(H9="nicht erforderlich","Entfällt",IF(AND(H9="vollständig",J9&lt;&gt;""),"Vollständig",IF(AND(H9="vollständig",J9=""),"Dokument fehlt",IF(AND(ISNUMBER(I9),I9&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M9" s="1" t="n"/>
       <c r="N9" s="1" t="n"/>
@@ -829,9 +831,10 @@
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="7" t="n"/>
       <c r="K10" s="7" t="n"/>
-      <c r="L10" s="1">
-        <f>IF(H10="nicht erforderlich","Entfällt",IF(AND(H10="vollständig",J10&lt;&gt;""),"Vollständig",IF(AND(H10="vollständig",J10=""),"Dokument fehlt",IF(AND(ISNUMBER(I10),I10&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M10" s="1" t="n"/>
       <c r="N10" s="1" t="n"/>
@@ -871,9 +874,10 @@
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="7" t="n"/>
       <c r="K11" s="7" t="n"/>
-      <c r="L11" s="1">
-        <f>IF(H11="nicht erforderlich","Entfällt",IF(AND(H11="vollständig",J11&lt;&gt;""),"Vollständig",IF(AND(H11="vollständig",J11=""),"Dokument fehlt",IF(AND(ISNUMBER(I11),I11&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M11" s="1" t="n"/>
       <c r="N11" s="1" t="n"/>
@@ -913,9 +917,10 @@
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="7" t="n"/>
       <c r="K12" s="7" t="n"/>
-      <c r="L12" s="1">
-        <f>IF(H12="nicht erforderlich","Entfällt",IF(AND(H12="vollständig",J12&lt;&gt;""),"Vollständig",IF(AND(H12="vollständig",J12=""),"Dokument fehlt",IF(AND(ISNUMBER(I12),I12&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M12" s="1" t="n"/>
       <c r="N12" s="1" t="n"/>
@@ -955,9 +960,10 @@
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="7" t="n"/>
       <c r="K13" s="7" t="n"/>
-      <c r="L13" s="1">
-        <f>IF(H13="nicht erforderlich","Entfällt",IF(AND(H13="vollständig",J13&lt;&gt;""),"Vollständig",IF(AND(H13="vollständig",J13=""),"Dokument fehlt",IF(AND(ISNUMBER(I13),I13&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M13" s="1" t="n"/>
       <c r="N13" s="1" t="n"/>
@@ -997,9 +1003,10 @@
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="7" t="n"/>
       <c r="K14" s="7" t="n"/>
-      <c r="L14" s="1">
-        <f>IF(H14="nicht erforderlich","Entfällt",IF(AND(H14="vollständig",J14&lt;&gt;""),"Vollständig",IF(AND(H14="vollständig",J14=""),"Dokument fehlt",IF(AND(ISNUMBER(I14),I14&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M14" s="1" t="n"/>
       <c r="N14" s="1" t="n"/>
@@ -1039,9 +1046,10 @@
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="7" t="n"/>
       <c r="K15" s="7" t="n"/>
-      <c r="L15" s="1">
-        <f>IF(H15="nicht erforderlich","Entfällt",IF(AND(H15="vollständig",J15&lt;&gt;""),"Vollständig",IF(AND(H15="vollständig",J15=""),"Dokument fehlt",IF(AND(ISNUMBER(I15),I15&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M15" s="1" t="n"/>
       <c r="N15" s="1" t="n"/>
@@ -1081,9 +1089,10 @@
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="7" t="n"/>
       <c r="K16" s="7" t="n"/>
-      <c r="L16" s="1">
-        <f>IF(H16="nicht erforderlich","Entfällt",IF(AND(H16="vollständig",J16&lt;&gt;""),"Vollständig",IF(AND(H16="vollständig",J16=""),"Dokument fehlt",IF(AND(ISNUMBER(I16),I16&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M16" s="1" t="n"/>
       <c r="N16" s="1" t="n"/>
@@ -1123,9 +1132,10 @@
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n"/>
-      <c r="L17" s="1">
-        <f>IF(H17="nicht erforderlich","Entfällt",IF(AND(H17="vollständig",J17&lt;&gt;""),"Vollständig",IF(AND(H17="vollständig",J17=""),"Dokument fehlt",IF(AND(ISNUMBER(I17),I17&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M17" s="1" t="n"/>
       <c r="N17" s="1" t="n"/>
@@ -1165,9 +1175,10 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="7" t="n"/>
       <c r="K18" s="7" t="n"/>
-      <c r="L18" s="1">
-        <f>IF(H18="nicht erforderlich","Entfällt",IF(AND(H18="vollständig",J18&lt;&gt;""),"Vollständig",IF(AND(H18="vollständig",J18=""),"Dokument fehlt",IF(AND(ISNUMBER(I18),I18&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M18" s="1" t="n"/>
       <c r="N18" s="1" t="n"/>
@@ -1207,9 +1218,10 @@
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="7" t="n"/>
-      <c r="L19" s="1">
-        <f>IF(H19="nicht erforderlich","Entfällt",IF(AND(H19="vollständig",J19&lt;&gt;""),"Vollständig",IF(AND(H19="vollständig",J19=""),"Dokument fehlt",IF(AND(ISNUMBER(I19),I19&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M19" s="1" t="n"/>
       <c r="N19" s="1" t="n"/>
@@ -1249,9 +1261,10 @@
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
-      <c r="L20" s="1">
-        <f>IF(H20="nicht erforderlich","Entfällt",IF(AND(H20="vollständig",J20&lt;&gt;""),"Vollständig",IF(AND(H20="vollständig",J20=""),"Dokument fehlt",IF(AND(ISNUMBER(I20),I20&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M20" s="1" t="n"/>
       <c r="N20" s="1" t="n"/>
@@ -1291,9 +1304,10 @@
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
-      <c r="L21" s="1">
-        <f>IF(H21="nicht erforderlich","Entfällt",IF(AND(H21="vollständig",J21&lt;&gt;""),"Vollständig",IF(AND(H21="vollständig",J21=""),"Dokument fehlt",IF(AND(ISNUMBER(I21),I21&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M21" s="1" t="n"/>
       <c r="N21" s="1" t="n"/>
@@ -1333,9 +1347,10 @@
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
-      <c r="L22" s="1">
-        <f>IF(H22="nicht erforderlich","Entfällt",IF(AND(H22="vollständig",J22&lt;&gt;""),"Vollständig",IF(AND(H22="vollständig",J22=""),"Dokument fehlt",IF(AND(ISNUMBER(I22),I22&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M22" s="1" t="n"/>
       <c r="N22" s="1" t="n"/>
@@ -1375,9 +1390,10 @@
       <c r="I23" s="8" t="n"/>
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
-      <c r="L23" s="1">
-        <f>IF(H23="nicht erforderlich","Entfällt",IF(AND(H23="vollständig",J23&lt;&gt;""),"Vollständig",IF(AND(H23="vollständig",J23=""),"Dokument fehlt",IF(AND(ISNUMBER(I23),I23&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M23" s="1" t="n"/>
       <c r="N23" s="1" t="n"/>
@@ -1417,9 +1433,10 @@
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
-      <c r="L24" s="1">
-        <f>IF(H24="nicht erforderlich","Entfällt",IF(AND(H24="vollständig",J24&lt;&gt;""),"Vollständig",IF(AND(H24="vollständig",J24=""),"Dokument fehlt",IF(AND(ISNUMBER(I24),I24&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M24" s="1" t="n"/>
       <c r="N24" s="1" t="n"/>
@@ -1459,9 +1476,10 @@
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
-      <c r="L25" s="1">
-        <f>IF(H25="nicht erforderlich","Entfällt",IF(AND(H25="vollständig",J25&lt;&gt;""),"Vollständig",IF(AND(H25="vollständig",J25=""),"Dokument fehlt",IF(AND(ISNUMBER(I25),I25&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M25" s="1" t="n"/>
       <c r="N25" s="1" t="n"/>
@@ -1501,9 +1519,10 @@
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
-      <c r="L26" s="1">
-        <f>IF(H26="nicht erforderlich","Entfällt",IF(AND(H26="vollständig",J26&lt;&gt;""),"Vollständig",IF(AND(H26="vollständig",J26=""),"Dokument fehlt",IF(AND(ISNUMBER(I26),I26&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M26" s="1" t="n"/>
       <c r="N26" s="1" t="n"/>
@@ -1543,9 +1562,10 @@
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
-      <c r="L27" s="1">
-        <f>IF(H27="nicht erforderlich","Entfällt",IF(AND(H27="vollständig",J27&lt;&gt;""),"Vollständig",IF(AND(H27="vollständig",J27=""),"Dokument fehlt",IF(AND(ISNUMBER(I27),I27&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M27" s="1" t="n"/>
       <c r="N27" s="1" t="n"/>
@@ -1585,9 +1605,10 @@
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
-      <c r="L28" s="1">
-        <f>IF(H28="nicht erforderlich","Entfällt",IF(AND(H28="vollständig",J28&lt;&gt;""),"Vollständig",IF(AND(H28="vollständig",J28=""),"Dokument fehlt",IF(AND(ISNUMBER(I28),I28&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M28" s="1" t="n"/>
       <c r="N28" s="1" t="n"/>
@@ -1627,9 +1648,10 @@
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
-      <c r="L29" s="1">
-        <f>IF(H29="nicht erforderlich","Entfällt",IF(AND(H29="vollständig",J29&lt;&gt;""),"Vollständig",IF(AND(H29="vollständig",J29=""),"Dokument fehlt",IF(AND(ISNUMBER(I29),I29&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L29" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M29" s="1" t="n"/>
       <c r="N29" s="1" t="n"/>
@@ -1669,9 +1691,10 @@
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
-      <c r="L30" s="1">
-        <f>IF(H30="nicht erforderlich","Entfällt",IF(AND(H30="vollständig",J30&lt;&gt;""),"Vollständig",IF(AND(H30="vollständig",J30=""),"Dokument fehlt",IF(AND(ISNUMBER(I30),I30&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M30" s="1" t="n"/>
       <c r="N30" s="1" t="n"/>
@@ -1711,9 +1734,10 @@
       <c r="I31" s="8" t="n"/>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
-      <c r="L31" s="1">
-        <f>IF(H31="nicht erforderlich","Entfällt",IF(AND(H31="vollständig",J31&lt;&gt;""),"Vollständig",IF(AND(H31="vollständig",J31=""),"Dokument fehlt",IF(AND(ISNUMBER(I31),I31&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M31" s="1" t="n"/>
       <c r="N31" s="1" t="n"/>
@@ -1753,9 +1777,10 @@
       <c r="I32" s="8" t="n"/>
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
-      <c r="L32" s="1">
-        <f>IF(H32="nicht erforderlich","Entfällt",IF(AND(H32="vollständig",J32&lt;&gt;""),"Vollständig",IF(AND(H32="vollständig",J32=""),"Dokument fehlt",IF(AND(ISNUMBER(I32),I32&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M32" s="1" t="n"/>
       <c r="N32" s="1" t="n"/>
@@ -1795,9 +1820,10 @@
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
-      <c r="L33" s="1">
-        <f>IF(H33="nicht erforderlich","Entfällt",IF(AND(H33="vollständig",J33&lt;&gt;""),"Vollständig",IF(AND(H33="vollständig",J33=""),"Dokument fehlt",IF(AND(ISNUMBER(I33),I33&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M33" s="1" t="n"/>
       <c r="N33" s="1" t="n"/>
@@ -1837,9 +1863,10 @@
       <c r="I34" s="8" t="n"/>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
-      <c r="L34" s="1">
-        <f>IF(H34="nicht erforderlich","Entfällt",IF(AND(H34="vollständig",J34&lt;&gt;""),"Vollständig",IF(AND(H34="vollständig",J34=""),"Dokument fehlt",IF(AND(ISNUMBER(I34),I34&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M34" s="1" t="n"/>
       <c r="N34" s="1" t="n"/>
@@ -1881,9 +1908,10 @@
       </c>
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
-      <c r="L35" s="1">
-        <f>IF(H35="nicht erforderlich","Entfällt",IF(AND(H35="vollständig",J35&lt;&gt;""),"Vollständig",IF(AND(H35="vollständig",J35=""),"Dokument fehlt",IF(AND(ISNUMBER(I35),I35&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M35" s="1" t="n"/>
       <c r="N35" s="1" t="n"/>
@@ -1923,9 +1951,10 @@
       <c r="I36" s="8" t="n"/>
       <c r="J36" s="7" t="n"/>
       <c r="K36" s="7" t="n"/>
-      <c r="L36" s="1">
-        <f>IF(H36="nicht erforderlich","Entfällt",IF(AND(H36="vollständig",J36&lt;&gt;""),"Vollständig",IF(AND(H36="vollständig",J36=""),"Dokument fehlt",IF(AND(ISNUMBER(I36),I36&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M36" s="1" t="n"/>
       <c r="N36" s="1" t="n"/>
@@ -1965,9 +1994,10 @@
       <c r="I37" s="8" t="n"/>
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
-      <c r="L37" s="1">
-        <f>IF(H37="nicht erforderlich","Entfällt",IF(AND(H37="vollständig",J37&lt;&gt;""),"Vollständig",IF(AND(H37="vollständig",J37=""),"Dokument fehlt",IF(AND(ISNUMBER(I37),I37&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L37" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M37" s="1" t="n"/>
       <c r="N37" s="1" t="n"/>
@@ -2007,9 +2037,10 @@
       <c r="I38" s="8" t="n"/>
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
-      <c r="L38" s="1">
-        <f>IF(H38="nicht erforderlich","Entfällt",IF(AND(H38="vollständig",J38&lt;&gt;""),"Vollständig",IF(AND(H38="vollständig",J38=""),"Dokument fehlt",IF(AND(ISNUMBER(I38),I38&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M38" s="1" t="n"/>
       <c r="N38" s="1" t="n"/>
@@ -2049,9 +2080,10 @@
       <c r="I39" s="8" t="n"/>
       <c r="J39" s="7" t="n"/>
       <c r="K39" s="7" t="n"/>
-      <c r="L39" s="1">
-        <f>IF(H39="nicht erforderlich","Entfällt",IF(AND(H39="vollständig",J39&lt;&gt;""),"Vollständig",IF(AND(H39="vollständig",J39=""),"Dokument fehlt",IF(AND(ISNUMBER(I39),I39&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M39" s="1" t="n"/>
       <c r="N39" s="1" t="n"/>
@@ -2091,9 +2123,10 @@
       <c r="I40" s="8" t="n"/>
       <c r="J40" s="7" t="n"/>
       <c r="K40" s="7" t="n"/>
-      <c r="L40" s="1">
-        <f>IF(H40="nicht erforderlich","Entfällt",IF(AND(H40="vollständig",J40&lt;&gt;""),"Vollständig",IF(AND(H40="vollständig",J40=""),"Dokument fehlt",IF(AND(ISNUMBER(I40),I40&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M40" s="1" t="n"/>
       <c r="N40" s="1" t="n"/>
@@ -2133,9 +2166,10 @@
       <c r="I41" s="8" t="n"/>
       <c r="J41" s="7" t="n"/>
       <c r="K41" s="7" t="n"/>
-      <c r="L41" s="1">
-        <f>IF(H41="nicht erforderlich","Entfällt",IF(AND(H41="vollständig",J41&lt;&gt;""),"Vollständig",IF(AND(H41="vollständig",J41=""),"Dokument fehlt",IF(AND(ISNUMBER(I41),I41&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M41" s="1" t="n"/>
       <c r="N41" s="1" t="n"/>
@@ -2175,9 +2209,10 @@
       <c r="I42" s="8" t="n"/>
       <c r="J42" s="7" t="n"/>
       <c r="K42" s="7" t="n"/>
-      <c r="L42" s="1">
-        <f>IF(H42="nicht erforderlich","Entfällt",IF(AND(H42="vollständig",J42&lt;&gt;""),"Vollständig",IF(AND(H42="vollständig",J42=""),"Dokument fehlt",IF(AND(ISNUMBER(I42),I42&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M42" s="1" t="n"/>
       <c r="N42" s="1" t="n"/>
@@ -2217,9 +2252,10 @@
       <c r="I43" s="8" t="n"/>
       <c r="J43" s="7" t="n"/>
       <c r="K43" s="7" t="n"/>
-      <c r="L43" s="1">
-        <f>IF(H43="nicht erforderlich","Entfällt",IF(AND(H43="vollständig",J43&lt;&gt;""),"Vollständig",IF(AND(H43="vollständig",J43=""),"Dokument fehlt",IF(AND(ISNUMBER(I43),I43&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M43" s="1" t="n"/>
       <c r="N43" s="1" t="n"/>
@@ -2259,9 +2295,10 @@
       <c r="I44" s="8" t="n"/>
       <c r="J44" s="7" t="n"/>
       <c r="K44" s="7" t="n"/>
-      <c r="L44" s="1">
-        <f>IF(H44="nicht erforderlich","Entfällt",IF(AND(H44="vollständig",J44&lt;&gt;""),"Vollständig",IF(AND(H44="vollständig",J44=""),"Dokument fehlt",IF(AND(ISNUMBER(I44),I44&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M44" s="1" t="n"/>
       <c r="N44" s="1" t="n"/>
@@ -2301,9 +2338,10 @@
       <c r="I45" s="8" t="n"/>
       <c r="J45" s="7" t="n"/>
       <c r="K45" s="7" t="n"/>
-      <c r="L45" s="1">
-        <f>IF(H45="nicht erforderlich","Entfällt",IF(AND(H45="vollständig",J45&lt;&gt;""),"Vollständig",IF(AND(H45="vollständig",J45=""),"Dokument fehlt",IF(AND(ISNUMBER(I45),I45&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M45" s="1" t="n"/>
       <c r="N45" s="1" t="n"/>
@@ -2343,9 +2381,10 @@
       <c r="I46" s="8" t="n"/>
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
-      <c r="L46" s="1">
-        <f>IF(H46="nicht erforderlich","Entfällt",IF(AND(H46="vollständig",J46&lt;&gt;""),"Vollständig",IF(AND(H46="vollständig",J46=""),"Dokument fehlt",IF(AND(ISNUMBER(I46),I46&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M46" s="1" t="n"/>
       <c r="N46" s="1" t="n"/>
@@ -2385,9 +2424,10 @@
       <c r="I47" s="8" t="n"/>
       <c r="J47" s="7" t="n"/>
       <c r="K47" s="7" t="n"/>
-      <c r="L47" s="1">
-        <f>IF(H47="nicht erforderlich","Entfällt",IF(AND(H47="vollständig",J47&lt;&gt;""),"Vollständig",IF(AND(H47="vollständig",J47=""),"Dokument fehlt",IF(AND(ISNUMBER(I47),I47&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M47" s="1" t="n"/>
       <c r="N47" s="1" t="n"/>
@@ -2427,9 +2467,10 @@
       <c r="I48" s="8" t="n"/>
       <c r="J48" s="7" t="n"/>
       <c r="K48" s="7" t="n"/>
-      <c r="L48" s="1">
-        <f>IF(H48="nicht erforderlich","Entfällt",IF(AND(H48="vollständig",J48&lt;&gt;""),"Vollständig",IF(AND(H48="vollständig",J48=""),"Dokument fehlt",IF(AND(ISNUMBER(I48),I48&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M48" s="1" t="n"/>
       <c r="N48" s="1" t="n"/>
@@ -2469,9 +2510,10 @@
       <c r="I49" s="8" t="n"/>
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
-      <c r="L49" s="1">
-        <f>IF(H49="nicht erforderlich","Entfällt",IF(AND(H49="vollständig",J49&lt;&gt;""),"Vollständig",IF(AND(H49="vollständig",J49=""),"Dokument fehlt",IF(AND(ISNUMBER(I49),I49&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M49" s="1" t="n"/>
       <c r="N49" s="1" t="n"/>
@@ -2511,9 +2553,10 @@
       <c r="I50" s="8" t="n"/>
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
-      <c r="L50" s="1">
-        <f>IF(H50="nicht erforderlich","Entfällt",IF(AND(H50="vollständig",J50&lt;&gt;""),"Vollständig",IF(AND(H50="vollständig",J50=""),"Dokument fehlt",IF(AND(ISNUMBER(I50),I50&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M50" s="1" t="n"/>
       <c r="N50" s="1" t="n"/>
@@ -2553,9 +2596,10 @@
       <c r="I51" s="8" t="n"/>
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
-      <c r="L51" s="1">
-        <f>IF(H51="nicht erforderlich","Entfällt",IF(AND(H51="vollständig",J51&lt;&gt;""),"Vollständig",IF(AND(H51="vollständig",J51=""),"Dokument fehlt",IF(AND(ISNUMBER(I51),I51&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M51" s="1" t="n"/>
       <c r="N51" s="1" t="n"/>
@@ -2595,9 +2639,10 @@
       <c r="I52" s="8" t="n"/>
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
-      <c r="L52" s="1">
-        <f>IF(H52="nicht erforderlich","Entfällt",IF(AND(H52="vollständig",J52&lt;&gt;""),"Vollständig",IF(AND(H52="vollständig",J52=""),"Dokument fehlt",IF(AND(ISNUMBER(I52),I52&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L52" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M52" s="1" t="n"/>
       <c r="N52" s="1" t="n"/>
@@ -2637,9 +2682,10 @@
       <c r="I53" s="8" t="n"/>
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
-      <c r="L53" s="1">
-        <f>IF(H53="nicht erforderlich","Entfällt",IF(AND(H53="vollständig",J53&lt;&gt;""),"Vollständig",IF(AND(H53="vollständig",J53=""),"Dokument fehlt",IF(AND(ISNUMBER(I53),I53&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M53" s="1" t="n"/>
       <c r="N53" s="1" t="n"/>
@@ -2679,9 +2725,10 @@
       <c r="I54" s="8" t="n"/>
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
-      <c r="L54" s="1">
-        <f>IF(H54="nicht erforderlich","Entfällt",IF(AND(H54="vollständig",J54&lt;&gt;""),"Vollständig",IF(AND(H54="vollständig",J54=""),"Dokument fehlt",IF(AND(ISNUMBER(I54),I54&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M54" s="1" t="n"/>
       <c r="N54" s="1" t="n"/>
@@ -2721,9 +2768,10 @@
       <c r="I55" s="8" t="n"/>
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
-      <c r="L55" s="1">
-        <f>IF(H55="nicht erforderlich","Entfällt",IF(AND(H55="vollständig",J55&lt;&gt;""),"Vollständig",IF(AND(H55="vollständig",J55=""),"Dokument fehlt",IF(AND(ISNUMBER(I55),I55&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M55" s="1" t="n"/>
       <c r="N55" s="1" t="n"/>
@@ -2763,9 +2811,10 @@
       <c r="I56" s="8" t="n"/>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
-      <c r="L56" s="1">
-        <f>IF(H56="nicht erforderlich","Entfällt",IF(AND(H56="vollständig",J56&lt;&gt;""),"Vollständig",IF(AND(H56="vollständig",J56=""),"Dokument fehlt",IF(AND(ISNUMBER(I56),I56&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M56" s="1" t="n"/>
       <c r="N56" s="1" t="n"/>
@@ -2805,9 +2854,10 @@
       <c r="I57" s="8" t="n"/>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
-      <c r="L57" s="1">
-        <f>IF(H57="nicht erforderlich","Entfällt",IF(AND(H57="vollständig",J57&lt;&gt;""),"Vollständig",IF(AND(H57="vollständig",J57=""),"Dokument fehlt",IF(AND(ISNUMBER(I57),I57&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M57" s="1" t="n"/>
       <c r="N57" s="1" t="n"/>
@@ -2847,9 +2897,10 @@
       <c r="I58" s="8" t="n"/>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
-      <c r="L58" s="1">
-        <f>IF(H58="nicht erforderlich","Entfällt",IF(AND(H58="vollständig",J58&lt;&gt;""),"Vollständig",IF(AND(H58="vollständig",J58=""),"Dokument fehlt",IF(AND(ISNUMBER(I58),I58&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M58" s="1" t="n"/>
       <c r="N58" s="1" t="n"/>
@@ -2889,9 +2940,10 @@
       <c r="I59" s="8" t="n"/>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
-      <c r="L59" s="1">
-        <f>IF(H59="nicht erforderlich","Entfällt",IF(AND(H59="vollständig",J59&lt;&gt;""),"Vollständig",IF(AND(H59="vollständig",J59=""),"Dokument fehlt",IF(AND(ISNUMBER(I59),I59&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M59" s="1" t="n"/>
       <c r="N59" s="1" t="n"/>
@@ -2931,9 +2983,10 @@
       <c r="I60" s="8" t="n"/>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
-      <c r="L60" s="1">
-        <f>IF(H60="nicht erforderlich","Entfällt",IF(AND(H60="vollständig",J60&lt;&gt;""),"Vollständig",IF(AND(H60="vollständig",J60=""),"Dokument fehlt",IF(AND(ISNUMBER(I60),I60&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L60" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
       <c r="M60" s="1" t="n"/>
       <c r="N60" s="1" t="n"/>
@@ -2971,9 +3024,10 @@
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="11" t="n"/>
       <c r="K61" s="11" t="n"/>
-      <c r="L61" s="9">
-        <f>IF(H61="nicht erforderlich","Entfällt",IF(AND(H61="vollständig",J61&lt;&gt;""),"Vollständig",IF(AND(H61="vollständig",J61=""),"Dokument fehlt",IF(AND(ISNUMBER(I61),I61&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="43" customHeight="1">
@@ -3008,9 +3062,10 @@
       <c r="I62" s="12" t="n"/>
       <c r="J62" s="11" t="n"/>
       <c r="K62" s="11" t="n"/>
-      <c r="L62" s="9">
-        <f>IF(H62="nicht erforderlich","Entfällt",IF(AND(H62="vollständig",J62&lt;&gt;""),"Vollständig",IF(AND(H62="vollständig",J62=""),"Dokument fehlt",IF(AND(ISNUMBER(I62),I62&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="43" customHeight="1">
@@ -3045,9 +3100,10 @@
       <c r="I63" s="12" t="n"/>
       <c r="J63" s="11" t="n"/>
       <c r="K63" s="11" t="n"/>
-      <c r="L63" s="9">
-        <f>IF(H63="nicht erforderlich","Entfällt",IF(AND(H63="vollständig",J63&lt;&gt;""),"Vollständig",IF(AND(H63="vollständig",J63=""),"Dokument fehlt",IF(AND(ISNUMBER(I63),I63&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="43" customHeight="1">
@@ -3082,9 +3138,10 @@
       <c r="I64" s="12" t="n"/>
       <c r="J64" s="11" t="n"/>
       <c r="K64" s="11" t="n"/>
-      <c r="L64" s="9">
-        <f>IF(H64="nicht erforderlich","Entfällt",IF(AND(H64="vollständig",J64&lt;&gt;""),"Vollständig",IF(AND(H64="vollständig",J64=""),"Dokument fehlt",IF(AND(ISNUMBER(I64),I64&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="43" customHeight="1">
@@ -3119,9 +3176,10 @@
       <c r="I65" s="12" t="n"/>
       <c r="J65" s="11" t="n"/>
       <c r="K65" s="11" t="n"/>
-      <c r="L65" s="9">
-        <f>IF(H65="nicht erforderlich","Entfällt",IF(AND(H65="vollständig",J65&lt;&gt;""),"Vollständig",IF(AND(H65="vollständig",J65=""),"Dokument fehlt",IF(AND(ISNUMBER(I65),I65&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="43" customHeight="1">
@@ -3156,9 +3214,10 @@
       <c r="I66" s="12" t="n"/>
       <c r="J66" s="11" t="n"/>
       <c r="K66" s="11" t="n"/>
-      <c r="L66" s="9">
-        <f>IF(H66="nicht erforderlich","Entfällt",IF(AND(H66="vollständig",J66&lt;&gt;""),"Vollständig",IF(AND(H66="vollständig",J66=""),"Dokument fehlt",IF(AND(ISNUMBER(I66),I66&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="43" customHeight="1">
@@ -3193,9 +3252,10 @@
       <c r="I67" s="12" t="n"/>
       <c r="J67" s="11" t="n"/>
       <c r="K67" s="11" t="n"/>
-      <c r="L67" s="9">
-        <f>IF(H67="nicht erforderlich","Entfällt",IF(AND(H67="vollständig",J67&lt;&gt;""),"Vollständig",IF(AND(H67="vollständig",J67=""),"Dokument fehlt",IF(AND(ISNUMBER(I67),I67&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="68" ht="43" customHeight="1">
@@ -3230,9 +3290,10 @@
       <c r="I68" s="12" t="n"/>
       <c r="J68" s="11" t="n"/>
       <c r="K68" s="11" t="n"/>
-      <c r="L68" s="9">
-        <f>IF(H68="nicht erforderlich","Entfällt",IF(AND(H68="vollständig",J68&lt;&gt;""),"Vollständig",IF(AND(H68="vollständig",J68=""),"Dokument fehlt",IF(AND(ISNUMBER(I68),I68&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="43" customHeight="1">
@@ -3267,9 +3328,10 @@
       <c r="I69" s="12" t="n"/>
       <c r="J69" s="11" t="n"/>
       <c r="K69" s="11" t="n"/>
-      <c r="L69" s="9">
-        <f>IF(H69="nicht erforderlich","Entfällt",IF(AND(H69="vollständig",J69&lt;&gt;""),"Vollständig",IF(AND(H69="vollständig",J69=""),"Dokument fehlt",IF(AND(ISNUMBER(I69),I69&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="43" customHeight="1">
@@ -3304,9 +3366,10 @@
       <c r="I70" s="12" t="n"/>
       <c r="J70" s="11" t="n"/>
       <c r="K70" s="11" t="n"/>
-      <c r="L70" s="9">
-        <f>IF(H70="nicht erforderlich","Entfällt",IF(AND(H70="vollständig",J70&lt;&gt;""),"Vollständig",IF(AND(H70="vollständig",J70=""),"Dokument fehlt",IF(AND(ISNUMBER(I70),I70&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="43" customHeight="1">
@@ -3341,9 +3404,10 @@
       <c r="I71" s="12" t="n"/>
       <c r="J71" s="11" t="n"/>
       <c r="K71" s="11" t="n"/>
-      <c r="L71" s="9">
-        <f>IF(H71="nicht erforderlich","Entfällt",IF(AND(H71="vollständig",J71&lt;&gt;""),"Vollständig",IF(AND(H71="vollständig",J71=""),"Dokument fehlt",IF(AND(ISNUMBER(I71),I71&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="43" customHeight="1">
@@ -3378,9 +3442,10 @@
       <c r="I72" s="12" t="n"/>
       <c r="J72" s="11" t="n"/>
       <c r="K72" s="11" t="n"/>
-      <c r="L72" s="9">
-        <f>IF(H72="nicht erforderlich","Entfällt",IF(AND(H72="vollständig",J72&lt;&gt;""),"Vollständig",IF(AND(H72="vollständig",J72=""),"Dokument fehlt",IF(AND(ISNUMBER(I72),I72&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="43" customHeight="1">
@@ -3415,9 +3480,10 @@
       <c r="I73" s="12" t="n"/>
       <c r="J73" s="11" t="n"/>
       <c r="K73" s="11" t="n"/>
-      <c r="L73" s="9">
-        <f>IF(H73="nicht erforderlich","Entfällt",IF(AND(H73="vollständig",J73&lt;&gt;""),"Vollständig",IF(AND(H73="vollständig",J73=""),"Dokument fehlt",IF(AND(ISNUMBER(I73),I73&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="43" customHeight="1">
@@ -3452,9 +3518,10 @@
       <c r="I74" s="12" t="n"/>
       <c r="J74" s="11" t="n"/>
       <c r="K74" s="11" t="n"/>
-      <c r="L74" s="9">
-        <f>IF(H74="nicht erforderlich","Entfällt",IF(AND(H74="vollständig",J74&lt;&gt;""),"Vollständig",IF(AND(H74="vollständig",J74=""),"Dokument fehlt",IF(AND(ISNUMBER(I74),I74&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="43" customHeight="1">
@@ -3489,9 +3556,10 @@
       <c r="I75" s="12" t="n"/>
       <c r="J75" s="11" t="n"/>
       <c r="K75" s="11" t="n"/>
-      <c r="L75" s="9">
-        <f>IF(H75="nicht erforderlich","Entfällt",IF(AND(H75="vollständig",J75&lt;&gt;""),"Vollständig",IF(AND(H75="vollständig",J75=""),"Dokument fehlt",IF(AND(ISNUMBER(I75),I75&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="43" customHeight="1">
@@ -3526,9 +3594,10 @@
       <c r="I76" s="12" t="n"/>
       <c r="J76" s="11" t="n"/>
       <c r="K76" s="11" t="n"/>
-      <c r="L76" s="9">
-        <f>IF(H76="nicht erforderlich","Entfällt",IF(AND(H76="vollständig",J76&lt;&gt;""),"Vollständig",IF(AND(H76="vollständig",J76=""),"Dokument fehlt",IF(AND(ISNUMBER(I76),I76&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="43" customHeight="1">
@@ -3563,9 +3632,10 @@
       <c r="I77" s="12" t="n"/>
       <c r="J77" s="11" t="n"/>
       <c r="K77" s="11" t="n"/>
-      <c r="L77" s="9">
-        <f>IF(H77="nicht erforderlich","Entfällt",IF(AND(H77="vollständig",J77&lt;&gt;""),"Vollständig",IF(AND(H77="vollständig",J77=""),"Dokument fehlt",IF(AND(ISNUMBER(I77),I77&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="43" customHeight="1">
@@ -3600,9 +3670,10 @@
       <c r="I78" s="12" t="n"/>
       <c r="J78" s="11" t="n"/>
       <c r="K78" s="11" t="n"/>
-      <c r="L78" s="9">
-        <f>IF(H78="nicht erforderlich","Entfällt",IF(AND(H78="vollständig",J78&lt;&gt;""),"Vollständig",IF(AND(H78="vollständig",J78=""),"Dokument fehlt",IF(AND(ISNUMBER(I78),I78&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="43" customHeight="1">
@@ -3637,9 +3708,10 @@
       <c r="I79" s="12" t="n"/>
       <c r="J79" s="11" t="n"/>
       <c r="K79" s="11" t="n"/>
-      <c r="L79" s="9">
-        <f>IF(H79="nicht erforderlich","Entfällt",IF(AND(H79="vollständig",J79&lt;&gt;""),"Vollständig",IF(AND(H79="vollständig",J79=""),"Dokument fehlt",IF(AND(ISNUMBER(I79),I79&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="43" customHeight="1">
@@ -3674,9 +3746,10 @@
       <c r="I80" s="12" t="n"/>
       <c r="J80" s="11" t="n"/>
       <c r="K80" s="11" t="n"/>
-      <c r="L80" s="9">
-        <f>IF(H80="nicht erforderlich","Entfällt",IF(AND(H80="vollständig",J80&lt;&gt;""),"Vollständig",IF(AND(H80="vollständig",J80=""),"Dokument fehlt",IF(AND(ISNUMBER(I80),I80&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="43" customHeight="1">
@@ -3711,9 +3784,10 @@
       <c r="I81" s="12" t="n"/>
       <c r="J81" s="11" t="n"/>
       <c r="K81" s="11" t="n"/>
-      <c r="L81" s="9">
-        <f>IF(H81="nicht erforderlich","Entfällt",IF(AND(H81="vollständig",J81&lt;&gt;""),"Vollständig",IF(AND(H81="vollständig",J81=""),"Dokument fehlt",IF(AND(ISNUMBER(I81),I81&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="43" customHeight="1">
@@ -3748,9 +3822,10 @@
       <c r="I82" s="12" t="n"/>
       <c r="J82" s="11" t="n"/>
       <c r="K82" s="11" t="n"/>
-      <c r="L82" s="9">
-        <f>IF(H82="nicht erforderlich","Entfällt",IF(AND(H82="vollständig",J82&lt;&gt;""),"Vollständig",IF(AND(H82="vollständig",J82=""),"Dokument fehlt",IF(AND(ISNUMBER(I82),I82&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="43" customHeight="1">
@@ -3785,9 +3860,10 @@
       <c r="I83" s="12" t="n"/>
       <c r="J83" s="11" t="n"/>
       <c r="K83" s="11" t="n"/>
-      <c r="L83" s="9">
-        <f>IF(H83="nicht erforderlich","Entfällt",IF(AND(H83="vollständig",J83&lt;&gt;""),"Vollständig",IF(AND(H83="vollständig",J83=""),"Dokument fehlt",IF(AND(ISNUMBER(I83),I83&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="43" customHeight="1">
@@ -3822,9 +3898,10 @@
       <c r="I84" s="12" t="n"/>
       <c r="J84" s="11" t="n"/>
       <c r="K84" s="11" t="n"/>
-      <c r="L84" s="9">
-        <f>IF(H84="nicht erforderlich","Entfällt",IF(AND(H84="vollständig",J84&lt;&gt;""),"Vollständig",IF(AND(H84="vollständig",J84=""),"Dokument fehlt",IF(AND(ISNUMBER(I84),I84&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="43" customHeight="1">
@@ -3859,9 +3936,10 @@
       <c r="I85" s="12" t="n"/>
       <c r="J85" s="11" t="n"/>
       <c r="K85" s="11" t="n"/>
-      <c r="L85" s="9">
-        <f>IF(H85="nicht erforderlich","Entfällt",IF(AND(H85="vollständig",J85&lt;&gt;""),"Vollständig",IF(AND(H85="vollständig",J85=""),"Dokument fehlt",IF(AND(ISNUMBER(I85),I85&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="43" customHeight="1">
@@ -3898,9 +3976,10 @@
       </c>
       <c r="J86" s="11" t="n"/>
       <c r="K86" s="11" t="n"/>
-      <c r="L86" s="9">
-        <f>IF(H86="nicht erforderlich","Entfällt",IF(AND(H86="vollständig",J86&lt;&gt;""),"Vollständig",IF(AND(H86="vollständig",J86=""),"Dokument fehlt",IF(AND(ISNUMBER(I86),I86&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="43" customHeight="1">
@@ -3935,9 +4014,10 @@
       <c r="I87" s="12" t="n"/>
       <c r="J87" s="11" t="n"/>
       <c r="K87" s="11" t="n"/>
-      <c r="L87" s="9">
-        <f>IF(H87="nicht erforderlich","Entfällt",IF(AND(H87="vollständig",J87&lt;&gt;""),"Vollständig",IF(AND(H87="vollständig",J87=""),"Dokument fehlt",IF(AND(ISNUMBER(I87),I87&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="43" customHeight="1">
@@ -3972,9 +4052,10 @@
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="11" t="n"/>
       <c r="K88" s="11" t="n"/>
-      <c r="L88" s="9">
-        <f>IF(H88="nicht erforderlich","Entfällt",IF(AND(H88="vollständig",J88&lt;&gt;""),"Vollständig",IF(AND(H88="vollständig",J88=""),"Dokument fehlt",IF(AND(ISNUMBER(I88),I88&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="43" customHeight="1">
@@ -4009,9 +4090,10 @@
       <c r="I89" s="12" t="n"/>
       <c r="J89" s="11" t="n"/>
       <c r="K89" s="11" t="n"/>
-      <c r="L89" s="9">
-        <f>IF(H89="nicht erforderlich","Entfällt",IF(AND(H89="vollständig",J89&lt;&gt;""),"Vollständig",IF(AND(H89="vollständig",J89=""),"Dokument fehlt",IF(AND(ISNUMBER(I89),I89&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="43" customHeight="1">
@@ -4046,11 +4128,14 @@
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="11" t="n"/>
       <c r="K90" s="11" t="n"/>
-      <c r="L90" s="9">
-        <f>IF(H90="nicht erforderlich","Entfällt",IF(AND(H90="vollständig",J90&lt;&gt;""),"Vollständig",IF(AND(H90="vollständig",J90=""),"Dokument fehlt",IF(AND(ISNUMBER(I90),I90&lt;'[Steuerung.xlsx]Steuerung'!$F$12),"Überfällig","Offen"))))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92"/>
     <row r="93">
       <c r="C93" t="inlineStr">
         <is>
